--- a/Assets/Excel/战斗实体配置表.xlsx
+++ b/Assets/Excel/战斗实体配置表.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="67">
   <si>
     <t>f_id</t>
   </si>
@@ -67,6 +67,9 @@
   </si>
   <si>
     <t>f_dmgTextYOffset</t>
+  </si>
+  <si>
+    <t>f_selMarkerYOffset</t>
   </si>
   <si>
     <t>int</t>
@@ -118,6 +121,9 @@
 基于角色脚底</t>
   </si>
   <si>
+    <t>目标选择标基于脚底Y轴偏移量</t>
+  </si>
+  <si>
     <t>战士</t>
   </si>
   <si>
@@ -149,6 +155,9 @@
   </si>
   <si>
     <t>f_weaknesses</t>
+  </si>
+  <si>
+    <t>f_bloodUiYOffset</t>
   </si>
   <si>
     <t>唯一ID</t>
@@ -192,6 +201,9 @@
   <si>
     <t>受伤文本高度偏移，
 基于脚底</t>
+  </si>
+  <si>
+    <t>怪物血量UI基于脚底Y轴偏移</t>
   </si>
   <si>
     <t>史莱姆</t>
@@ -1243,7 +1255,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -1255,9 +1267,10 @@
     <col min="7" max="7" width="14.625" customWidth="1"/>
     <col min="8" max="12" width="15" customWidth="1"/>
     <col min="13" max="13" width="21.25" customWidth="1"/>
+    <col min="14" max="14" width="28.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="2" customFormat="1" ht="22" customHeight="1" spans="1:13">
+    <row r="1" s="2" customFormat="1" ht="22" customHeight="1" spans="1:14">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -1297,304 +1310,57 @@
       <c r="M1" s="8" t="s">
         <v>12</v>
       </c>
+      <c r="N1" s="8" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" s="2" customFormat="1" ht="20" customHeight="1" spans="1:13">
+    <row r="2" s="2" customFormat="1" ht="20" customHeight="1" spans="1:14">
       <c r="A2" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B2" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="F2" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="I2" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" s="8" t="s">
+      <c r="J2" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="K2" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="J2" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="8" t="s">
-        <v>13</v>
-      </c>
       <c r="L2" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="M2" s="8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" s="2" customFormat="1" ht="18" customHeight="1" spans="1:13">
-      <c r="A3" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="8"/>
-      <c r="J3" s="8"/>
-      <c r="K3" s="8"/>
-      <c r="L3" s="8"/>
-      <c r="M3" s="8"/>
-    </row>
-    <row r="4" s="2" customFormat="1" ht="86" customHeight="1" spans="1:13">
-      <c r="A4" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="H4" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I4" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="J4" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="K4" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="L4" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="M4" s="13" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="5" s="4" customFormat="1" ht="39" customHeight="1" spans="1:13">
-      <c r="A5" s="4">
-        <v>1</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E5" s="4">
-        <v>1</v>
-      </c>
-      <c r="F5" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="H5" s="4">
-        <v>500</v>
-      </c>
-      <c r="I5" s="4">
-        <v>100</v>
-      </c>
-      <c r="J5" s="4">
-        <v>100</v>
-      </c>
-      <c r="K5" s="4">
-        <v>100</v>
-      </c>
-      <c r="L5" s="4">
-        <v>50</v>
-      </c>
-      <c r="M5" s="4">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="6" s="4" customFormat="1" ht="35" customHeight="1" spans="1:13">
-      <c r="A6" s="4">
-        <v>2</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="E6" s="4">
-        <v>2</v>
-      </c>
-      <c r="F6" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="H6" s="4">
-        <v>300</v>
-      </c>
-      <c r="I6" s="4">
-        <v>70</v>
-      </c>
-      <c r="J6" s="4">
-        <v>150</v>
-      </c>
-      <c r="K6" s="4">
-        <v>100</v>
-      </c>
-      <c r="L6" s="4">
-        <v>80</v>
-      </c>
-      <c r="M6" s="4">
-        <v>200</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:N6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5"/>
-  <cols>
-    <col min="1" max="1" width="11" customWidth="1"/>
-    <col min="2" max="2" width="12.5" customWidth="1"/>
-    <col min="3" max="3" width="16.875" customWidth="1"/>
-    <col min="4" max="4" width="20" customWidth="1"/>
-    <col min="5" max="5" width="14.875" customWidth="1"/>
-    <col min="6" max="6" width="108.375" customWidth="1"/>
-    <col min="7" max="7" width="11.5" customWidth="1"/>
-    <col min="8" max="11" width="15" customWidth="1"/>
-    <col min="12" max="13" width="21.5" customWidth="1"/>
-    <col min="14" max="14" width="18.25" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" s="1" customFormat="1" ht="24" customHeight="1" spans="1:14">
-      <c r="A1" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="M1" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="N1" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" s="2" customFormat="1" ht="26" customHeight="1" spans="1:14">
-      <c r="A2" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" s="8" t="s">
         <v>14</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="J2" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="L2" s="8" t="s">
-        <v>13</v>
       </c>
       <c r="M2" s="8" t="s">
         <v>14</v>
       </c>
       <c r="N2" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
-    <row r="3" s="2" customFormat="1" ht="25" customHeight="1" spans="1:14">
-      <c r="A3" s="7" t="s">
-        <v>15</v>
+    <row r="3" s="2" customFormat="1" ht="18" customHeight="1" spans="1:14">
+      <c r="A3" s="8" t="s">
+        <v>16</v>
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
@@ -1610,74 +1376,359 @@
       <c r="M3" s="8"/>
       <c r="N3" s="8"/>
     </row>
-    <row r="4" s="3" customFormat="1" ht="60" customHeight="1" spans="1:14">
-      <c r="A4" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="G4" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="H4" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="I4" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="J4" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="K4" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="L4" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="M4" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="N4" s="11" t="s">
-        <v>53</v>
+    <row r="4" s="2" customFormat="1" ht="86" customHeight="1" spans="1:14">
+      <c r="A4" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="K4" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="M4" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="N4" s="8" t="s">
+        <v>30</v>
       </c>
     </row>
-    <row r="5" s="4" customFormat="1" ht="86" customHeight="1" spans="1:14">
+    <row r="5" s="4" customFormat="1" ht="39" customHeight="1" spans="1:14">
       <c r="A5" s="4">
         <v>1</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>54</v>
+        <v>31</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="E5" s="4">
         <v>1</v>
       </c>
       <c r="F5" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="H5" s="4">
+        <v>500</v>
+      </c>
+      <c r="I5" s="4">
+        <v>100</v>
+      </c>
+      <c r="J5" s="4">
+        <v>100</v>
+      </c>
+      <c r="K5" s="4">
+        <v>100</v>
+      </c>
+      <c r="L5" s="4">
+        <v>50</v>
+      </c>
+      <c r="M5" s="4">
+        <v>200</v>
+      </c>
+      <c r="N5" s="4">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="6" s="4" customFormat="1" ht="35" customHeight="1" spans="1:14">
+      <c r="A6" s="4">
+        <v>2</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E6" s="4">
+        <v>2</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="H6" s="4">
+        <v>300</v>
+      </c>
+      <c r="I6" s="4">
+        <v>70</v>
+      </c>
+      <c r="J6" s="4">
+        <v>150</v>
+      </c>
+      <c r="K6" s="4">
+        <v>100</v>
+      </c>
+      <c r="L6" s="4">
+        <v>80</v>
+      </c>
+      <c r="M6" s="4">
+        <v>200</v>
+      </c>
+      <c r="N6" s="4">
+        <v>80</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:P6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5"/>
+  <cols>
+    <col min="1" max="1" width="11" customWidth="1"/>
+    <col min="2" max="2" width="12.5" customWidth="1"/>
+    <col min="3" max="3" width="16.875" customWidth="1"/>
+    <col min="4" max="4" width="20" customWidth="1"/>
+    <col min="5" max="5" width="14.875" customWidth="1"/>
+    <col min="6" max="6" width="108.375" customWidth="1"/>
+    <col min="7" max="7" width="11.5" customWidth="1"/>
+    <col min="8" max="11" width="15" customWidth="1"/>
+    <col min="12" max="13" width="21.5" customWidth="1"/>
+    <col min="14" max="14" width="18.25" customWidth="1"/>
+    <col min="15" max="15" width="28.625" customWidth="1"/>
+    <col min="16" max="16" width="26.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" ht="24" customHeight="1" spans="1:16">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="M1" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="N1" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" s="6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2" s="2" customFormat="1" ht="26" customHeight="1" spans="1:16">
+      <c r="A2" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K2" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="M2" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="N2" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="O2" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="P2" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" s="2" customFormat="1" ht="25" customHeight="1" spans="1:16">
+      <c r="A3" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="8"/>
+      <c r="K3" s="8"/>
+      <c r="L3" s="8"/>
+      <c r="M3" s="8"/>
+      <c r="N3" s="8"/>
+      <c r="O3" s="8"/>
+      <c r="P3" s="8"/>
+    </row>
+    <row r="4" s="3" customFormat="1" ht="60" customHeight="1" spans="1:16">
+      <c r="A4" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="H4" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="I4" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="J4" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="K4" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="L4" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="M4" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="N4" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="O4" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="P4" s="10" t="s">
         <v>57</v>
+      </c>
+    </row>
+    <row r="5" s="4" customFormat="1" ht="86" customHeight="1" spans="1:16">
+      <c r="A5" s="4">
+        <v>1</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E5" s="4">
+        <v>1</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>61</v>
       </c>
       <c r="G5" s="4">
         <v>101</v>
       </c>
       <c r="H5" s="4">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="I5" s="4">
         <v>80</v>
@@ -1692,36 +1743,42 @@
         <v>50</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="N5" s="4">
         <v>75</v>
       </c>
+      <c r="O5" s="4">
+        <v>50</v>
+      </c>
+      <c r="P5" s="4">
+        <v>200</v>
+      </c>
     </row>
-    <row r="6" s="4" customFormat="1" ht="78" customHeight="1" spans="1:14">
+    <row r="6" s="4" customFormat="1" ht="78" customHeight="1" spans="1:16">
       <c r="A6" s="4">
         <v>2</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E6" s="4">
         <v>2</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G6" s="4">
         <v>102</v>
       </c>
       <c r="H6" s="4">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="I6" s="4">
         <v>250</v>
@@ -1736,10 +1793,16 @@
         <v>75</v>
       </c>
       <c r="M6" s="4" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="N6" s="4">
         <v>75</v>
+      </c>
+      <c r="O6" s="4">
+        <v>50</v>
+      </c>
+      <c r="P6" s="4">
+        <v>200</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Excel/战斗实体配置表.xlsx
+++ b/Assets/Excel/战斗实体配置表.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="81">
   <si>
     <t>f_id</t>
   </si>
@@ -151,6 +151,30 @@
     <t>20,21,22</t>
   </si>
   <si>
+    <t>牧师</t>
+  </si>
+  <si>
+    <t>Icon_Priest</t>
+  </si>
+  <si>
+    <t>擅长治疗，辅助型</t>
+  </si>
+  <si>
+    <t>30,31,32</t>
+  </si>
+  <si>
+    <t>枪手</t>
+  </si>
+  <si>
+    <t>Icon_Gunman</t>
+  </si>
+  <si>
+    <t>擅长爆发输出</t>
+  </si>
+  <si>
+    <t>40,41,42</t>
+  </si>
+  <si>
     <t>f_baseToughness</t>
   </si>
   <si>
@@ -231,6 +255,24 @@
   </si>
   <si>
     <t>1,2,3</t>
+  </si>
+  <si>
+    <t>宝箱怪</t>
+  </si>
+  <si>
+    <t>Icon_Chest</t>
+  </si>
+  <si>
+    <t>里面可能有宝藏</t>
+  </si>
+  <si>
+    <t>深渊法师</t>
+  </si>
+  <si>
+    <t>Icon_AbyssalMage</t>
+  </si>
+  <si>
+    <t>邪恶的力量</t>
   </si>
 </sst>
 </file>
@@ -1255,8 +1297,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5"/>
+  <dimension ref="A1:N8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
     <col min="2" max="2" width="12.1083333333333" customWidth="1"/>
@@ -1508,6 +1550,94 @@
         <v>80</v>
       </c>
     </row>
+    <row r="7" s="4" customFormat="1" ht="38" customHeight="1" spans="1:14">
+      <c r="A7" s="4">
+        <v>3</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E7" s="4">
+        <v>3</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="H7" s="4">
+        <v>200</v>
+      </c>
+      <c r="I7" s="4">
+        <v>70</v>
+      </c>
+      <c r="J7" s="4">
+        <v>50</v>
+      </c>
+      <c r="K7" s="4">
+        <v>100</v>
+      </c>
+      <c r="L7" s="4">
+        <v>60</v>
+      </c>
+      <c r="M7" s="4">
+        <v>200</v>
+      </c>
+      <c r="N7" s="4">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8" s="4" customFormat="1" ht="42" customHeight="1" spans="1:14">
+      <c r="A8" s="4">
+        <v>4</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E8" s="4">
+        <v>4</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="H8" s="4">
+        <v>250</v>
+      </c>
+      <c r="I8" s="4">
+        <v>70</v>
+      </c>
+      <c r="J8" s="4">
+        <v>200</v>
+      </c>
+      <c r="K8" s="4">
+        <v>90</v>
+      </c>
+      <c r="L8" s="4">
+        <v>90</v>
+      </c>
+      <c r="M8" s="4">
+        <v>200</v>
+      </c>
+      <c r="N8" s="4">
+        <v>100</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -1518,8 +1648,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5"/>
+  <dimension ref="A1:P8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
     <col min="2" max="2" width="12.5" customWidth="1"/>
@@ -1570,10 +1700,10 @@
         <v>10</v>
       </c>
       <c r="L1" s="6" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="M1" s="6" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="N1" s="6" t="s">
         <v>12</v>
@@ -1582,7 +1712,7 @@
         <v>13</v>
       </c>
       <c r="P1" s="6" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" s="2" customFormat="1" ht="26" customHeight="1" spans="1:16">
@@ -1657,52 +1787,52 @@
     </row>
     <row r="4" s="3" customFormat="1" ht="60" customHeight="1" spans="1:16">
       <c r="A4" s="9" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="J4" s="10" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="K4" s="10" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="L4" s="10" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="M4" s="10" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="N4" s="11" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="O4" s="10" t="s">
         <v>30</v>
       </c>
       <c r="P4" s="10" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" s="4" customFormat="1" ht="86" customHeight="1" spans="1:16">
@@ -1710,25 +1840,25 @@
         <v>1</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="E5" s="4">
         <v>1</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="G5" s="4">
         <v>101</v>
       </c>
       <c r="H5" s="4">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="I5" s="4">
         <v>80</v>
@@ -1743,7 +1873,7 @@
         <v>50</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="N5" s="4">
         <v>75</v>
@@ -1760,25 +1890,25 @@
         <v>2</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="E6" s="4">
         <v>2</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="G6" s="4">
         <v>102</v>
       </c>
       <c r="H6" s="4">
-        <v>1000</v>
+        <v>350</v>
       </c>
       <c r="I6" s="4">
         <v>250</v>
@@ -1793,7 +1923,7 @@
         <v>75</v>
       </c>
       <c r="M6" s="4" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="N6" s="4">
         <v>75</v>
@@ -1803,6 +1933,106 @@
       </c>
       <c r="P6" s="4">
         <v>200</v>
+      </c>
+    </row>
+    <row r="7" s="4" customFormat="1" ht="54" customHeight="1" spans="1:16">
+      <c r="A7" s="4">
+        <v>3</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="E7" s="4">
+        <v>3</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="G7" s="4">
+        <v>103</v>
+      </c>
+      <c r="H7" s="4">
+        <v>500</v>
+      </c>
+      <c r="I7" s="4">
+        <v>300</v>
+      </c>
+      <c r="J7" s="4">
+        <v>50</v>
+      </c>
+      <c r="K7" s="4">
+        <v>80</v>
+      </c>
+      <c r="L7" s="4">
+        <v>100</v>
+      </c>
+      <c r="M7" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="N7" s="4">
+        <v>75</v>
+      </c>
+      <c r="O7" s="4">
+        <v>50</v>
+      </c>
+      <c r="P7" s="4">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="8" s="4" customFormat="1" ht="63" customHeight="1" spans="1:16">
+      <c r="A8" s="4">
+        <v>4</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="E8" s="4">
+        <v>4</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="G8" s="4">
+        <v>104</v>
+      </c>
+      <c r="H8" s="4">
+        <v>3000</v>
+      </c>
+      <c r="I8" s="4">
+        <v>150</v>
+      </c>
+      <c r="J8" s="4">
+        <v>200</v>
+      </c>
+      <c r="K8" s="4">
+        <v>110</v>
+      </c>
+      <c r="L8" s="4">
+        <v>200</v>
+      </c>
+      <c r="M8" s="4">
+        <v>1</v>
+      </c>
+      <c r="N8" s="4">
+        <v>75</v>
+      </c>
+      <c r="O8" s="4">
+        <v>50</v>
+      </c>
+      <c r="P8" s="4">
+        <v>250</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Excel/战斗实体配置表.xlsx
+++ b/Assets/Excel/战斗实体配置表.xlsx
@@ -93,7 +93,13 @@
     <t>角色描述</t>
   </si>
   <si>
-    <t>角色属性类型</t>
+    <t>角色属性类型
+0：无
+1：火
+2：冰
+3：物理
+4：量子
+5：风</t>
   </si>
   <si>
     <t>角色战斗所需组件名称</t>
@@ -1418,7 +1424,7 @@
       <c r="M3" s="8"/>
       <c r="N3" s="8"/>
     </row>
-    <row r="4" s="2" customFormat="1" ht="86" customHeight="1" spans="1:14">
+    <row r="4" s="2" customFormat="1" ht="101" customHeight="1" spans="1:14">
       <c r="A4" s="8" t="s">
         <v>17</v>
       </c>
@@ -1431,7 +1437,7 @@
       <c r="D4" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="13" t="s">
         <v>21</v>
       </c>
       <c r="F4" s="8" t="s">
@@ -1485,13 +1491,13 @@
         <v>35</v>
       </c>
       <c r="H5" s="4">
-        <v>500</v>
+        <v>3000</v>
       </c>
       <c r="I5" s="4">
         <v>100</v>
       </c>
       <c r="J5" s="4">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="K5" s="4">
         <v>100</v>
@@ -1529,13 +1535,13 @@
         <v>39</v>
       </c>
       <c r="H6" s="4">
-        <v>300</v>
+        <v>2000</v>
       </c>
       <c r="I6" s="4">
         <v>70</v>
       </c>
       <c r="J6" s="4">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="K6" s="4">
         <v>100</v>
@@ -1858,7 +1864,7 @@
         <v>101</v>
       </c>
       <c r="H5" s="4">
-        <v>200</v>
+        <v>3000</v>
       </c>
       <c r="I5" s="4">
         <v>80</v>
@@ -1908,7 +1914,7 @@
         <v>102</v>
       </c>
       <c r="H6" s="4">
-        <v>350</v>
+        <v>2000</v>
       </c>
       <c r="I6" s="4">
         <v>250</v>

--- a/Assets/Excel/战斗实体配置表.xlsx
+++ b/Assets/Excel/战斗实体配置表.xlsx
@@ -1579,7 +1579,7 @@
         <v>43</v>
       </c>
       <c r="H7" s="4">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="I7" s="4">
         <v>70</v>

--- a/Assets/Excel/战斗实体配置表.xlsx
+++ b/Assets/Excel/战斗实体配置表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255" activeTab="1"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="RoleInfo" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="74">
   <si>
     <t>f_id</t>
   </si>
@@ -64,12 +64,6 @@
   </si>
   <si>
     <t>f_maxEnergy</t>
-  </si>
-  <si>
-    <t>f_dmgTextYOffset</t>
-  </si>
-  <si>
-    <t>f_selMarkerYOffset</t>
   </si>
   <si>
     <t>int</t>
@@ -123,13 +117,6 @@
     <t>角色最大能量</t>
   </si>
   <si>
-    <t>角色受伤文本高度偏移，
-基于角色脚底</t>
-  </si>
-  <si>
-    <t>目标选择标基于脚底Y轴偏移量</t>
-  </si>
-  <si>
     <t>战士</t>
   </si>
   <si>
@@ -187,9 +174,6 @@
     <t>f_weaknesses</t>
   </si>
   <si>
-    <t>f_bloodUiYOffset</t>
-  </si>
-  <si>
     <t>唯一ID</t>
   </si>
   <si>
@@ -227,13 +211,6 @@
   </si>
   <si>
     <t>弱点类型</t>
-  </si>
-  <si>
-    <t>受伤文本高度偏移，
-基于脚底</t>
-  </si>
-  <si>
-    <t>怪物血量UI基于脚底Y轴偏移</t>
   </si>
   <si>
     <t>史莱姆</t>
@@ -949,7 +926,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -982,9 +959,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1303,7 +1277,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:L8"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -1314,11 +1288,9 @@
     <col min="6" max="6" width="90.875" customWidth="1"/>
     <col min="7" max="7" width="14.625" customWidth="1"/>
     <col min="8" max="12" width="15" customWidth="1"/>
-    <col min="13" max="13" width="21.25" customWidth="1"/>
-    <col min="14" max="14" width="28.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="2" customFormat="1" ht="22" customHeight="1" spans="1:14">
+    <row r="1" s="2" customFormat="1" ht="22" customHeight="1" spans="1:12">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -1355,60 +1327,360 @@
       <c r="L1" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="8" t="s">
+    </row>
+    <row r="2" s="2" customFormat="1" ht="20" customHeight="1" spans="1:12">
+      <c r="A2" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="8" t="s">
+      <c r="B2" s="8" t="s">
         <v>13</v>
       </c>
+      <c r="C2" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="J2" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="K2" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="L2" s="8" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="2" s="2" customFormat="1" ht="20" customHeight="1" spans="1:14">
-      <c r="A2" s="8" t="s">
+    <row r="3" s="2" customFormat="1" ht="18" customHeight="1" spans="1:12">
+      <c r="A3" s="8" t="s">
         <v>14</v>
       </c>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="8"/>
+      <c r="K3" s="8"/>
+      <c r="L3" s="8"/>
+    </row>
+    <row r="4" s="2" customFormat="1" ht="101" customHeight="1" spans="1:12">
+      <c r="A4" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="K4" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" s="4" customFormat="1" ht="39" customHeight="1" spans="1:12">
+      <c r="A5" s="4">
+        <v>1</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" s="4">
+        <v>1</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H5" s="4">
+        <v>3000</v>
+      </c>
+      <c r="I5" s="4">
+        <v>100</v>
+      </c>
+      <c r="J5" s="4">
+        <v>200</v>
+      </c>
+      <c r="K5" s="4">
+        <v>100</v>
+      </c>
+      <c r="L5" s="4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" s="4" customFormat="1" ht="35" customHeight="1" spans="1:12">
+      <c r="A6" s="4">
+        <v>2</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" s="4">
+        <v>2</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="H6" s="4">
+        <v>2000</v>
+      </c>
+      <c r="I6" s="4">
+        <v>70</v>
+      </c>
+      <c r="J6" s="4">
+        <v>300</v>
+      </c>
+      <c r="K6" s="4">
+        <v>100</v>
+      </c>
+      <c r="L6" s="4">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="7" s="4" customFormat="1" ht="38" customHeight="1" spans="1:12">
+      <c r="A7" s="4">
+        <v>3</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E7" s="4">
+        <v>3</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="H7" s="4">
+        <v>1000</v>
+      </c>
+      <c r="I7" s="4">
+        <v>70</v>
+      </c>
+      <c r="J7" s="4">
+        <v>50</v>
+      </c>
+      <c r="K7" s="4">
+        <v>100</v>
+      </c>
+      <c r="L7" s="4">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8" s="4" customFormat="1" ht="42" customHeight="1" spans="1:12">
+      <c r="A8" s="4">
+        <v>4</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E8" s="4">
+        <v>4</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="H8" s="4">
+        <v>250</v>
+      </c>
+      <c r="I8" s="4">
+        <v>70</v>
+      </c>
+      <c r="J8" s="4">
+        <v>200</v>
+      </c>
+      <c r="K8" s="4">
+        <v>90</v>
+      </c>
+      <c r="L8" s="4">
+        <v>90</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:M8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7"/>
+  <cols>
+    <col min="1" max="1" width="11" customWidth="1"/>
+    <col min="2" max="2" width="12.5" customWidth="1"/>
+    <col min="3" max="3" width="16.875" customWidth="1"/>
+    <col min="4" max="4" width="20" customWidth="1"/>
+    <col min="5" max="5" width="14.875" customWidth="1"/>
+    <col min="6" max="6" width="108.375" customWidth="1"/>
+    <col min="7" max="7" width="11.5" customWidth="1"/>
+    <col min="8" max="11" width="15" customWidth="1"/>
+    <col min="12" max="13" width="21.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" ht="24" customHeight="1" spans="1:13">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="M1" s="6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" s="2" customFormat="1" ht="26" customHeight="1" spans="1:13">
+      <c r="A2" s="7" t="s">
+        <v>12</v>
+      </c>
       <c r="B2" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E2" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="J2" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="K2" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="L2" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="M2" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" s="2" customFormat="1" ht="25" customHeight="1" spans="1:13">
+      <c r="A3" s="7" t="s">
         <v>14</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="J2" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K2" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="M2" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="N2" s="8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" s="2" customFormat="1" ht="18" customHeight="1" spans="1:14">
-      <c r="A3" s="8" t="s">
-        <v>16</v>
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
@@ -1422,607 +1694,203 @@
       <c r="K3" s="8"/>
       <c r="L3" s="8"/>
       <c r="M3" s="8"/>
-      <c r="N3" s="8"/>
     </row>
-    <row r="4" s="2" customFormat="1" ht="101" customHeight="1" spans="1:14">
-      <c r="A4" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="H4" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="I4" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="J4" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="K4" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="L4" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="M4" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="N4" s="8" t="s">
-        <v>30</v>
+    <row r="4" s="3" customFormat="1" ht="60" customHeight="1" spans="1:13">
+      <c r="A4" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="H4" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="I4" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="J4" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="K4" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="L4" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="M4" s="10" t="s">
+        <v>58</v>
       </c>
     </row>
-    <row r="5" s="4" customFormat="1" ht="39" customHeight="1" spans="1:14">
+    <row r="5" s="4" customFormat="1" ht="86" customHeight="1" spans="1:13">
       <c r="A5" s="4">
         <v>1</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>31</v>
+        <v>59</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>33</v>
+        <v>61</v>
       </c>
       <c r="E5" s="4">
         <v>1</v>
       </c>
-      <c r="F5" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>35</v>
+      <c r="F5" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="G5" s="4">
+        <v>101</v>
       </c>
       <c r="H5" s="4">
         <v>3000</v>
       </c>
       <c r="I5" s="4">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="J5" s="4">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="K5" s="4">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="L5" s="4">
         <v>50</v>
       </c>
-      <c r="M5" s="4">
-        <v>200</v>
-      </c>
-      <c r="N5" s="4">
-        <v>80</v>
+      <c r="M5" s="4" t="s">
+        <v>63</v>
       </c>
     </row>
-    <row r="6" s="4" customFormat="1" ht="35" customHeight="1" spans="1:14">
+    <row r="6" s="4" customFormat="1" ht="78" customHeight="1" spans="1:13">
       <c r="A6" s="4">
         <v>2</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>37</v>
+        <v>65</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="E6" s="4">
         <v>2</v>
       </c>
-      <c r="F6" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>39</v>
+      <c r="F6" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="G6" s="4">
+        <v>102</v>
       </c>
       <c r="H6" s="4">
         <v>2000</v>
       </c>
       <c r="I6" s="4">
-        <v>70</v>
+        <v>250</v>
       </c>
       <c r="J6" s="4">
-        <v>300</v>
+        <v>25</v>
       </c>
       <c r="K6" s="4">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="L6" s="4">
-        <v>80</v>
-      </c>
-      <c r="M6" s="4">
-        <v>200</v>
-      </c>
-      <c r="N6" s="4">
-        <v>80</v>
+        <v>75</v>
+      </c>
+      <c r="M6" s="4" t="s">
+        <v>67</v>
       </c>
     </row>
-    <row r="7" s="4" customFormat="1" ht="38" customHeight="1" spans="1:14">
+    <row r="7" s="4" customFormat="1" ht="54" customHeight="1" spans="1:13">
       <c r="A7" s="4">
         <v>3</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>41</v>
+        <v>69</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="E7" s="4">
         <v>3</v>
       </c>
-      <c r="F7" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>43</v>
+      <c r="F7" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="G7" s="4">
+        <v>103</v>
       </c>
       <c r="H7" s="4">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="I7" s="4">
-        <v>70</v>
+        <v>300</v>
       </c>
       <c r="J7" s="4">
         <v>50</v>
       </c>
       <c r="K7" s="4">
+        <v>80</v>
+      </c>
+      <c r="L7" s="4">
         <v>100</v>
       </c>
-      <c r="L7" s="4">
-        <v>60</v>
-      </c>
-      <c r="M7" s="4">
-        <v>200</v>
-      </c>
-      <c r="N7" s="4">
-        <v>80</v>
+      <c r="M7" s="4" t="s">
+        <v>63</v>
       </c>
     </row>
-    <row r="8" s="4" customFormat="1" ht="42" customHeight="1" spans="1:14">
+    <row r="8" s="4" customFormat="1" ht="63" customHeight="1" spans="1:13">
       <c r="A8" s="4">
         <v>4</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>46</v>
+        <v>73</v>
       </c>
       <c r="E8" s="4">
         <v>4</v>
       </c>
-      <c r="F8" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>47</v>
+      <c r="F8" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="G8" s="4">
+        <v>104</v>
       </c>
       <c r="H8" s="4">
-        <v>250</v>
+        <v>3000</v>
       </c>
       <c r="I8" s="4">
-        <v>70</v>
+        <v>150</v>
       </c>
       <c r="J8" s="4">
         <v>200</v>
       </c>
       <c r="K8" s="4">
-        <v>90</v>
-      </c>
-      <c r="L8" s="4">
-        <v>90</v>
-      </c>
-      <c r="M8" s="4">
-        <v>200</v>
-      </c>
-      <c r="N8" s="4">
-        <v>100</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:P8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7"/>
-  <cols>
-    <col min="1" max="1" width="11" customWidth="1"/>
-    <col min="2" max="2" width="12.5" customWidth="1"/>
-    <col min="3" max="3" width="16.875" customWidth="1"/>
-    <col min="4" max="4" width="20" customWidth="1"/>
-    <col min="5" max="5" width="14.875" customWidth="1"/>
-    <col min="6" max="6" width="108.375" customWidth="1"/>
-    <col min="7" max="7" width="11.5" customWidth="1"/>
-    <col min="8" max="11" width="15" customWidth="1"/>
-    <col min="12" max="13" width="21.5" customWidth="1"/>
-    <col min="14" max="14" width="18.25" customWidth="1"/>
-    <col min="15" max="15" width="28.625" customWidth="1"/>
-    <col min="16" max="16" width="26.625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" s="1" customFormat="1" ht="24" customHeight="1" spans="1:16">
-      <c r="A1" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="M1" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="N1" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="O1" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="P1" s="6" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="2" s="2" customFormat="1" ht="26" customHeight="1" spans="1:16">
-      <c r="A2" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="J2" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K2" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="M2" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="N2" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="O2" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="P2" s="8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" s="2" customFormat="1" ht="25" customHeight="1" spans="1:16">
-      <c r="A3" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="8"/>
-      <c r="J3" s="8"/>
-      <c r="K3" s="8"/>
-      <c r="L3" s="8"/>
-      <c r="M3" s="8"/>
-      <c r="N3" s="8"/>
-      <c r="O3" s="8"/>
-      <c r="P3" s="8"/>
-    </row>
-    <row r="4" s="3" customFormat="1" ht="60" customHeight="1" spans="1:16">
-      <c r="A4" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="G4" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="H4" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="I4" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="J4" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="K4" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="L4" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="M4" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="N4" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="O4" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="P4" s="10" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="5" s="4" customFormat="1" ht="86" customHeight="1" spans="1:16">
-      <c r="A5" s="4">
-        <v>1</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="E5" s="4">
-        <v>1</v>
-      </c>
-      <c r="F5" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="G5" s="4">
-        <v>101</v>
-      </c>
-      <c r="H5" s="4">
-        <v>3000</v>
-      </c>
-      <c r="I5" s="4">
-        <v>80</v>
-      </c>
-      <c r="J5" s="4">
-        <v>50</v>
-      </c>
-      <c r="K5" s="4">
-        <v>90</v>
-      </c>
-      <c r="L5" s="4">
-        <v>50</v>
-      </c>
-      <c r="M5" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="N5" s="4">
-        <v>75</v>
-      </c>
-      <c r="O5" s="4">
-        <v>50</v>
-      </c>
-      <c r="P5" s="4">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="6" s="4" customFormat="1" ht="78" customHeight="1" spans="1:16">
-      <c r="A6" s="4">
-        <v>2</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="E6" s="4">
-        <v>2</v>
-      </c>
-      <c r="F6" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="G6" s="4">
-        <v>102</v>
-      </c>
-      <c r="H6" s="4">
-        <v>2000</v>
-      </c>
-      <c r="I6" s="4">
-        <v>250</v>
-      </c>
-      <c r="J6" s="4">
-        <v>25</v>
-      </c>
-      <c r="K6" s="4">
-        <v>85</v>
-      </c>
-      <c r="L6" s="4">
-        <v>75</v>
-      </c>
-      <c r="M6" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="N6" s="4">
-        <v>75</v>
-      </c>
-      <c r="O6" s="4">
-        <v>50</v>
-      </c>
-      <c r="P6" s="4">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="7" s="4" customFormat="1" ht="54" customHeight="1" spans="1:16">
-      <c r="A7" s="4">
-        <v>3</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="E7" s="4">
-        <v>3</v>
-      </c>
-      <c r="F7" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="G7" s="4">
-        <v>103</v>
-      </c>
-      <c r="H7" s="4">
-        <v>500</v>
-      </c>
-      <c r="I7" s="4">
-        <v>300</v>
-      </c>
-      <c r="J7" s="4">
-        <v>50</v>
-      </c>
-      <c r="K7" s="4">
-        <v>80</v>
-      </c>
-      <c r="L7" s="4">
-        <v>100</v>
-      </c>
-      <c r="M7" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="N7" s="4">
-        <v>75</v>
-      </c>
-      <c r="O7" s="4">
-        <v>50</v>
-      </c>
-      <c r="P7" s="4">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="8" s="4" customFormat="1" ht="63" customHeight="1" spans="1:16">
-      <c r="A8" s="4">
-        <v>4</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="E8" s="4">
-        <v>4</v>
-      </c>
-      <c r="F8" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="G8" s="4">
-        <v>104</v>
-      </c>
-      <c r="H8" s="4">
-        <v>3000</v>
-      </c>
-      <c r="I8" s="4">
-        <v>150</v>
-      </c>
-      <c r="J8" s="4">
-        <v>200</v>
-      </c>
-      <c r="K8" s="4">
         <v>110</v>
       </c>
       <c r="L8" s="4">
@@ -2030,15 +1898,6 @@
       </c>
       <c r="M8" s="4">
         <v>1</v>
-      </c>
-      <c r="N8" s="4">
-        <v>75</v>
-      </c>
-      <c r="O8" s="4">
-        <v>50</v>
-      </c>
-      <c r="P8" s="4">
-        <v>250</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Excel/战斗实体配置表.xlsx
+++ b/Assets/Excel/战斗实体配置表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12255" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="RoleInfo" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="75">
   <si>
     <t>f_id</t>
   </si>
@@ -256,6 +256,9 @@
   </si>
   <si>
     <t>邪恶的力量</t>
+  </si>
+  <si>
+    <t>103,104</t>
   </si>
 </sst>
 </file>
@@ -926,7 +929,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -942,26 +945,41 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1291,132 +1309,132 @@
   </cols>
   <sheetData>
     <row r="1" s="2" customFormat="1" ht="22" customHeight="1" spans="1:12">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="J1" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="K1" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="L1" s="10" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="2" s="2" customFormat="1" ht="20" customHeight="1" spans="1:12">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="G2" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="H2" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="I2" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="J2" s="8" t="s">
+      <c r="J2" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="K2" s="8" t="s">
+      <c r="K2" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="L2" s="8" t="s">
+      <c r="L2" s="10" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="3" s="2" customFormat="1" ht="18" customHeight="1" spans="1:12">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="8"/>
-      <c r="J3" s="8"/>
-      <c r="K3" s="8"/>
-      <c r="L3" s="8"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
     </row>
     <row r="4" s="2" customFormat="1" ht="101" customHeight="1" spans="1:12">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F4" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="8" t="s">
+      <c r="G4" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="H4" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="I4" s="8" t="s">
+      <c r="I4" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="J4" s="8" t="s">
+      <c r="J4" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="K4" s="8" t="s">
+      <c r="K4" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="L4" s="8" t="s">
+      <c r="L4" s="10" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1436,7 +1454,7 @@
       <c r="E5" s="4">
         <v>1</v>
       </c>
-      <c r="F5" s="11" t="s">
+      <c r="F5" s="15" t="s">
         <v>30</v>
       </c>
       <c r="G5" s="4" t="s">
@@ -1474,7 +1492,7 @@
       <c r="E6" s="4">
         <v>2</v>
       </c>
-      <c r="F6" s="11" t="s">
+      <c r="F6" s="15" t="s">
         <v>30</v>
       </c>
       <c r="G6" s="4" t="s">
@@ -1512,7 +1530,7 @@
       <c r="E7" s="4">
         <v>3</v>
       </c>
-      <c r="F7" s="11" t="s">
+      <c r="F7" s="15" t="s">
         <v>30</v>
       </c>
       <c r="G7" s="4" t="s">
@@ -1550,7 +1568,7 @@
       <c r="E8" s="4">
         <v>4</v>
       </c>
-      <c r="F8" s="11" t="s">
+      <c r="F8" s="15" t="s">
         <v>30</v>
       </c>
       <c r="G8" s="4" t="s">
@@ -1591,148 +1609,148 @@
     <col min="4" max="4" width="20" customWidth="1"/>
     <col min="5" max="5" width="14.875" customWidth="1"/>
     <col min="6" max="6" width="108.375" customWidth="1"/>
-    <col min="7" max="7" width="11.5" customWidth="1"/>
+    <col min="7" max="7" width="11.5" style="5" customWidth="1"/>
     <col min="8" max="11" width="15" customWidth="1"/>
     <col min="12" max="13" width="21.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="24" customHeight="1" spans="1:13">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="K1" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="L1" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="M1" s="7" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="2" s="2" customFormat="1" ht="26" customHeight="1" spans="1:13">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="G2" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="H2" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="I2" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="J2" s="8" t="s">
+      <c r="J2" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="K2" s="8" t="s">
+      <c r="K2" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="L2" s="8" t="s">
+      <c r="L2" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="M2" s="8" t="s">
+      <c r="M2" s="10" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" s="2" customFormat="1" ht="25" customHeight="1" spans="1:13">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="8"/>
-      <c r="J3" s="8"/>
-      <c r="K3" s="8"/>
-      <c r="L3" s="8"/>
-      <c r="M3" s="8"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="10"/>
     </row>
     <row r="4" s="3" customFormat="1" ht="60" customHeight="1" spans="1:13">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="F4" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="G4" s="10" t="s">
+      <c r="G4" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="H4" s="10" t="s">
+      <c r="H4" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="I4" s="10" t="s">
+      <c r="I4" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="J4" s="10" t="s">
+      <c r="J4" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="K4" s="10" t="s">
+      <c r="K4" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="L4" s="10" t="s">
+      <c r="L4" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="M4" s="10" t="s">
+      <c r="M4" s="13" t="s">
         <v>58</v>
       </c>
     </row>
@@ -1752,10 +1770,10 @@
       <c r="E5" s="4">
         <v>1</v>
       </c>
-      <c r="F5" s="11" t="s">
+      <c r="F5" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="G5" s="4">
+      <c r="G5" s="16">
         <v>101</v>
       </c>
       <c r="H5" s="4">
@@ -1793,10 +1811,10 @@
       <c r="E6" s="4">
         <v>2</v>
       </c>
-      <c r="F6" s="11" t="s">
+      <c r="F6" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="G6" s="4">
+      <c r="G6" s="16">
         <v>102</v>
       </c>
       <c r="H6" s="4">
@@ -1834,10 +1852,10 @@
       <c r="E7" s="4">
         <v>3</v>
       </c>
-      <c r="F7" s="11" t="s">
+      <c r="F7" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="G7" s="4">
+      <c r="G7" s="16">
         <v>103</v>
       </c>
       <c r="H7" s="4">
@@ -1875,11 +1893,11 @@
       <c r="E8" s="4">
         <v>4</v>
       </c>
-      <c r="F8" s="11" t="s">
+      <c r="F8" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="G8" s="4">
-        <v>104</v>
+      <c r="G8" s="16" t="s">
+        <v>74</v>
       </c>
       <c r="H8" s="4">
         <v>3000</v>
@@ -1891,7 +1909,7 @@
         <v>200</v>
       </c>
       <c r="K8" s="4">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="L8" s="4">
         <v>200</v>

--- a/Assets/Excel/战斗实体配置表.xlsx
+++ b/Assets/Excel/战斗实体配置表.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="78">
   <si>
     <t>f_id</t>
   </si>
@@ -174,6 +174,12 @@
     <t>f_weaknesses</t>
   </si>
   <si>
+    <t>f_statesUiY0ffset</t>
+  </si>
+  <si>
+    <t>float</t>
+  </si>
+  <si>
     <t>唯一ID</t>
   </si>
   <si>
@@ -213,6 +219,9 @@
     <t>弱点类型</t>
   </si>
   <si>
+    <t>怪物状态UIY轴偏移</t>
+  </si>
+  <si>
     <t>史莱姆</t>
   </si>
   <si>
@@ -258,7 +267,7 @@
     <t>邪恶的力量</t>
   </si>
   <si>
-    <t>103,104</t>
+    <t>103,104,105,106</t>
   </si>
 </sst>
 </file>
@@ -946,7 +955,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -955,7 +964,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -964,7 +973,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -973,13 +982,13 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1600,7 +1609,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -1612,9 +1621,10 @@
     <col min="7" max="7" width="11.5" style="5" customWidth="1"/>
     <col min="8" max="11" width="15" customWidth="1"/>
     <col min="12" max="13" width="21.5" customWidth="1"/>
+    <col min="14" max="14" width="19.375" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="24" customHeight="1" spans="1:13">
+    <row r="1" s="1" customFormat="1" ht="24" customHeight="1" spans="1:14">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -1654,8 +1664,11 @@
       <c r="M1" s="7" t="s">
         <v>45</v>
       </c>
+      <c r="N1" s="7" t="s">
+        <v>46</v>
+      </c>
     </row>
-    <row r="2" s="2" customFormat="1" ht="26" customHeight="1" spans="1:13">
+    <row r="2" s="2" customFormat="1" ht="26" customHeight="1" spans="1:14">
       <c r="A2" s="9" t="s">
         <v>12</v>
       </c>
@@ -1695,8 +1708,11 @@
       <c r="M2" s="10" t="s">
         <v>13</v>
       </c>
+      <c r="N2" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
-    <row r="3" s="2" customFormat="1" ht="25" customHeight="1" spans="1:13">
+    <row r="3" s="2" customFormat="1" ht="25" customHeight="1" spans="1:14">
       <c r="A3" s="9" t="s">
         <v>14</v>
       </c>
@@ -1712,66 +1728,70 @@
       <c r="K3" s="10"/>
       <c r="L3" s="10"/>
       <c r="M3" s="10"/>
+      <c r="N3" s="10"/>
     </row>
-    <row r="4" s="3" customFormat="1" ht="60" customHeight="1" spans="1:13">
+    <row r="4" s="3" customFormat="1" ht="60" customHeight="1" spans="1:14">
       <c r="A4" s="12" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="H4" s="13" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="I4" s="13" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="J4" s="13" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K4" s="13" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="L4" s="13" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="M4" s="13" t="s">
-        <v>58</v>
+        <v>60</v>
+      </c>
+      <c r="N4" s="13" t="s">
+        <v>61</v>
       </c>
     </row>
-    <row r="5" s="4" customFormat="1" ht="86" customHeight="1" spans="1:13">
+    <row r="5" s="4" customFormat="1" ht="86" customHeight="1" spans="1:14">
       <c r="A5" s="4">
         <v>1</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E5" s="4">
         <v>1</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G5" s="16">
         <v>101</v>
@@ -1792,27 +1812,30 @@
         <v>50</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>63</v>
+        <v>66</v>
+      </c>
+      <c r="N5" s="4">
+        <v>1.75</v>
       </c>
     </row>
-    <row r="6" s="4" customFormat="1" ht="78" customHeight="1" spans="1:13">
+    <row r="6" s="4" customFormat="1" ht="78" customHeight="1" spans="1:14">
       <c r="A6" s="4">
         <v>2</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E6" s="4">
         <v>2</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G6" s="16">
         <v>102</v>
@@ -1833,27 +1856,30 @@
         <v>75</v>
       </c>
       <c r="M6" s="4" t="s">
-        <v>67</v>
+        <v>70</v>
+      </c>
+      <c r="N6" s="4">
+        <v>1.75</v>
       </c>
     </row>
-    <row r="7" s="4" customFormat="1" ht="54" customHeight="1" spans="1:13">
+    <row r="7" s="4" customFormat="1" ht="54" customHeight="1" spans="1:14">
       <c r="A7" s="4">
         <v>3</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E7" s="4">
         <v>3</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G7" s="16">
         <v>103</v>
@@ -1874,30 +1900,33 @@
         <v>100</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>63</v>
+        <v>66</v>
+      </c>
+      <c r="N7" s="4">
+        <v>1.75</v>
       </c>
     </row>
-    <row r="8" s="4" customFormat="1" ht="63" customHeight="1" spans="1:13">
+    <row r="8" s="4" customFormat="1" ht="63" customHeight="1" spans="1:14">
       <c r="A8" s="4">
         <v>4</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="E8" s="4">
         <v>4</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G8" s="16" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="H8" s="4">
         <v>3000</v>
@@ -1916,6 +1945,9 @@
       </c>
       <c r="M8" s="4">
         <v>1</v>
+      </c>
+      <c r="N8" s="4">
+        <v>2.5</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Excel/战斗实体配置表.xlsx
+++ b/Assets/Excel/战斗实体配置表.xlsx
@@ -1797,7 +1797,7 @@
         <v>101</v>
       </c>
       <c r="H5" s="4">
-        <v>3000</v>
+        <v>100</v>
       </c>
       <c r="I5" s="4">
         <v>80</v>
@@ -1841,7 +1841,7 @@
         <v>102</v>
       </c>
       <c r="H6" s="4">
-        <v>2000</v>
+        <v>100</v>
       </c>
       <c r="I6" s="4">
         <v>250</v>
@@ -1885,7 +1885,7 @@
         <v>103</v>
       </c>
       <c r="H7" s="4">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="I7" s="4">
         <v>300</v>
@@ -1929,7 +1929,7 @@
         <v>77</v>
       </c>
       <c r="H8" s="4">
-        <v>3000</v>
+        <v>200</v>
       </c>
       <c r="I8" s="4">
         <v>150</v>

--- a/Assets/Excel/战斗实体配置表.xlsx
+++ b/Assets/Excel/战斗实体配置表.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="88">
   <si>
     <t>f_id</t>
   </si>
@@ -64,6 +64,9 @@
   </si>
   <si>
     <t>f_maxEnergy</t>
+  </si>
+  <si>
+    <t>f_animProfile</t>
   </si>
   <si>
     <t>int</t>
@@ -117,6 +120,9 @@
     <t>角色最大能量</t>
   </si>
   <si>
+    <t>角色使用的动画配置文件</t>
+  </si>
+  <si>
     <t>战士</t>
   </si>
   <si>
@@ -132,6 +138,9 @@
     <t>10,11,12</t>
   </si>
   <si>
+    <t>WarriorAnimationConfigCollection</t>
+  </si>
+  <si>
     <t>法师</t>
   </si>
   <si>
@@ -144,6 +153,9 @@
     <t>20,21,22</t>
   </si>
   <si>
+    <t>WizardAnimationConfigCollection</t>
+  </si>
+  <si>
     <t>牧师</t>
   </si>
   <si>
@@ -156,6 +168,9 @@
     <t>30,31,32</t>
   </si>
   <si>
+    <t>PriestAnimationConfigCollection</t>
+  </si>
+  <si>
     <t>枪手</t>
   </si>
   <si>
@@ -222,6 +237,9 @@
     <t>怪物状态UIY轴偏移</t>
   </si>
   <si>
+    <t>怪物使用的动画配置文件</t>
+  </si>
+  <si>
     <t>史莱姆</t>
   </si>
   <si>
@@ -237,6 +255,9 @@
     <t>1,2,3,4</t>
   </si>
   <si>
+    <t>SlimeAnimationCommonConfig</t>
+  </si>
+  <si>
     <t>甲壳虫</t>
   </si>
   <si>
@@ -249,6 +270,9 @@
     <t>1,2,3</t>
   </si>
   <si>
+    <t>TurtleShellAnimationCommonConfig</t>
+  </si>
+  <si>
     <t>宝箱怪</t>
   </si>
   <si>
@@ -258,6 +282,9 @@
     <t>里面可能有宝藏</t>
   </si>
   <si>
+    <t>null</t>
+  </si>
+  <si>
     <t>深渊法师</t>
   </si>
   <si>
@@ -268,6 +295,9 @@
   </si>
   <si>
     <t>103,104,105,106</t>
+  </si>
+  <si>
+    <t>AbyssalMageAnimationConfigCollection</t>
   </si>
 </sst>
 </file>
@@ -1304,7 +1334,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -1315,9 +1345,10 @@
     <col min="6" max="6" width="90.875" customWidth="1"/>
     <col min="7" max="7" width="14.625" customWidth="1"/>
     <col min="8" max="12" width="15" customWidth="1"/>
+    <col min="13" max="13" width="36" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="2" customFormat="1" ht="22" customHeight="1" spans="1:12">
+    <row r="1" s="2" customFormat="1" ht="22" customHeight="1" spans="1:13">
       <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
@@ -1354,48 +1385,54 @@
       <c r="L1" s="10" t="s">
         <v>11</v>
       </c>
+      <c r="M1" s="10" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="2" s="2" customFormat="1" ht="20" customHeight="1" spans="1:12">
+    <row r="2" s="2" customFormat="1" ht="20" customHeight="1" spans="1:13">
       <c r="A2" s="10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B2" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="F2" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="I2" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" s="10" t="s">
+      <c r="J2" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="K2" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="I2" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="J2" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="K2" s="10" t="s">
-        <v>12</v>
-      </c>
       <c r="L2" s="10" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="M2" s="10" t="s">
+        <v>14</v>
       </c>
     </row>
-    <row r="3" s="2" customFormat="1" ht="18" customHeight="1" spans="1:12">
+    <row r="3" s="2" customFormat="1" ht="18" customHeight="1" spans="1:13">
       <c r="A3" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B3" s="10"/>
       <c r="C3" s="10"/>
@@ -1408,66 +1445,70 @@
       <c r="J3" s="10"/>
       <c r="K3" s="10"/>
       <c r="L3" s="10"/>
+      <c r="M3" s="10"/>
     </row>
-    <row r="4" s="2" customFormat="1" ht="101" customHeight="1" spans="1:12">
+    <row r="4" s="2" customFormat="1" ht="101" customHeight="1" spans="1:13">
       <c r="A4" s="10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J4" s="10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K4" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L4" s="10" t="s">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="M4" s="10" t="s">
+        <v>28</v>
       </c>
     </row>
-    <row r="5" s="4" customFormat="1" ht="39" customHeight="1" spans="1:12">
+    <row r="5" s="4" customFormat="1" ht="39" customHeight="1" spans="1:13">
       <c r="A5" s="4">
         <v>1</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E5" s="4">
         <v>1</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H5" s="4">
         <v>3000</v>
@@ -1484,28 +1525,31 @@
       <c r="L5" s="4">
         <v>50</v>
       </c>
+      <c r="M5" s="4" t="s">
+        <v>34</v>
+      </c>
     </row>
-    <row r="6" s="4" customFormat="1" ht="35" customHeight="1" spans="1:12">
+    <row r="6" s="4" customFormat="1" ht="35" customHeight="1" spans="1:13">
       <c r="A6" s="4">
         <v>2</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E6" s="4">
         <v>2</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H6" s="4">
         <v>2000</v>
@@ -1522,28 +1566,31 @@
       <c r="L6" s="4">
         <v>80</v>
       </c>
+      <c r="M6" s="4" t="s">
+        <v>39</v>
+      </c>
     </row>
-    <row r="7" s="4" customFormat="1" ht="38" customHeight="1" spans="1:12">
+    <row r="7" s="4" customFormat="1" ht="38" customHeight="1" spans="1:13">
       <c r="A7" s="4">
         <v>3</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E7" s="4">
         <v>3</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="H7" s="4">
         <v>1000</v>
@@ -1560,28 +1607,31 @@
       <c r="L7" s="4">
         <v>60</v>
       </c>
+      <c r="M7" s="4" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="8" s="4" customFormat="1" ht="42" customHeight="1" spans="1:12">
+    <row r="8" s="4" customFormat="1" ht="42" customHeight="1" spans="1:13">
       <c r="A8" s="4">
         <v>4</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E8" s="4">
         <v>4</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="H8" s="4">
         <v>250</v>
@@ -1609,7 +1659,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:O8"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -1622,9 +1672,10 @@
     <col min="8" max="11" width="15" customWidth="1"/>
     <col min="12" max="13" width="21.5" customWidth="1"/>
     <col min="14" max="14" width="19.375" style="4" customWidth="1"/>
+    <col min="15" max="15" width="40.375" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="24" customHeight="1" spans="1:14">
+    <row r="1" s="1" customFormat="1" ht="24" customHeight="1" spans="1:15">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -1659,62 +1710,68 @@
         <v>10</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="M1" s="7" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="N1" s="7" t="s">
-        <v>46</v>
+        <v>51</v>
+      </c>
+      <c r="O1" s="7" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="2" s="2" customFormat="1" ht="26" customHeight="1" spans="1:14">
+    <row r="2" s="2" customFormat="1" ht="26" customHeight="1" spans="1:15">
       <c r="A2" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B2" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="F2" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="I2" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" s="10" t="s">
+      <c r="J2" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="11" t="s">
+      <c r="K2" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="I2" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="J2" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="K2" s="10" t="s">
-        <v>12</v>
-      </c>
       <c r="L2" s="10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M2" s="10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N2" s="10" t="s">
-        <v>47</v>
+        <v>52</v>
+      </c>
+      <c r="O2" s="10" t="s">
+        <v>14</v>
       </c>
     </row>
-    <row r="3" s="2" customFormat="1" ht="25" customHeight="1" spans="1:14">
+    <row r="3" s="2" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A3" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B3" s="10"/>
       <c r="C3" s="10"/>
@@ -1729,69 +1786,73 @@
       <c r="L3" s="10"/>
       <c r="M3" s="10"/>
       <c r="N3" s="10"/>
+      <c r="O3" s="10"/>
     </row>
-    <row r="4" s="3" customFormat="1" ht="60" customHeight="1" spans="1:14">
+    <row r="4" s="3" customFormat="1" ht="60" customHeight="1" spans="1:15">
       <c r="A4" s="12" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="H4" s="13" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="I4" s="13" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="J4" s="13" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="K4" s="13" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="L4" s="13" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="M4" s="13" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="N4" s="13" t="s">
-        <v>61</v>
+        <v>66</v>
+      </c>
+      <c r="O4" s="13" t="s">
+        <v>67</v>
       </c>
     </row>
-    <row r="5" s="4" customFormat="1" ht="86" customHeight="1" spans="1:14">
+    <row r="5" s="4" customFormat="1" ht="86" customHeight="1" spans="1:15">
       <c r="A5" s="4">
         <v>1</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="E5" s="4">
         <v>1</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="G5" s="16">
         <v>101</v>
@@ -1812,30 +1873,33 @@
         <v>50</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N5" s="4">
         <v>1.75</v>
       </c>
+      <c r="O5" s="4" t="s">
+        <v>73</v>
+      </c>
     </row>
-    <row r="6" s="4" customFormat="1" ht="78" customHeight="1" spans="1:14">
+    <row r="6" s="4" customFormat="1" ht="78" customHeight="1" spans="1:15">
       <c r="A6" s="4">
         <v>2</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="E6" s="4">
         <v>2</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="G6" s="16">
         <v>102</v>
@@ -1856,30 +1920,33 @@
         <v>75</v>
       </c>
       <c r="M6" s="4" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="N6" s="4">
         <v>1.75</v>
       </c>
+      <c r="O6" s="4" t="s">
+        <v>78</v>
+      </c>
     </row>
-    <row r="7" s="4" customFormat="1" ht="54" customHeight="1" spans="1:14">
+    <row r="7" s="4" customFormat="1" ht="54" customHeight="1" spans="1:15">
       <c r="A7" s="4">
         <v>3</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="E7" s="4">
         <v>3</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="G7" s="16">
         <v>103</v>
@@ -1900,33 +1967,36 @@
         <v>100</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N7" s="4">
         <v>1.75</v>
       </c>
+      <c r="O7" s="4" t="s">
+        <v>82</v>
+      </c>
     </row>
-    <row r="8" s="4" customFormat="1" ht="63" customHeight="1" spans="1:14">
+    <row r="8" s="4" customFormat="1" ht="63" customHeight="1" spans="1:15">
       <c r="A8" s="4">
         <v>4</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="E8" s="4">
         <v>4</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="G8" s="16" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H8" s="4">
         <v>200</v>
@@ -1948,6 +2018,9 @@
       </c>
       <c r="N8" s="4">
         <v>2.5</v>
+      </c>
+      <c r="O8" s="4" t="s">
+        <v>87</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Excel/战斗实体配置表.xlsx
+++ b/Assets/Excel/战斗实体配置表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255" activeTab="1"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="RoleInfo" sheetId="1" r:id="rId1"/>
@@ -132,7 +132,7 @@
     <t>攻防兼备，均衡型</t>
   </si>
   <si>
-    <t>BattleAnimationComponent,PlayerSkillComponent,PlayerPropertyComponent,StatusComponent</t>
+    <t>BattleAnimationComponent,PlayerSkillComponent,PlayerPropertyComponent,StatusComponent,AnimatorComponent</t>
   </si>
   <si>
     <t>10,11,12</t>
@@ -249,7 +249,7 @@
     <t>黏糊糊...</t>
   </si>
   <si>
-    <t>BattleAnimationComponent,MonsterSkillComponent,MonsterPropertyComponent,ToughnessComponent,StatusComponent</t>
+    <t>BattleAnimationComponent,MonsterSkillComponent,MonsterPropertyComponent,ToughnessComponent,StatusComponent,AnimatorComponent</t>
   </si>
   <si>
     <t>1,2,3,4</t>
@@ -1667,7 +1667,7 @@
     <col min="3" max="3" width="16.875" customWidth="1"/>
     <col min="4" max="4" width="20" customWidth="1"/>
     <col min="5" max="5" width="14.875" customWidth="1"/>
-    <col min="6" max="6" width="108.375" customWidth="1"/>
+    <col min="6" max="6" width="108.25" customWidth="1"/>
     <col min="7" max="7" width="11.5" style="5" customWidth="1"/>
     <col min="8" max="11" width="15" customWidth="1"/>
     <col min="12" max="13" width="21.5" customWidth="1"/>

--- a/Assets/Excel/战斗实体配置表.xlsx
+++ b/Assets/Excel/战斗实体配置表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12255" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="RoleInfo" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="101">
   <si>
     <t>f_id</t>
   </si>
@@ -67,6 +67,9 @@
   </si>
   <si>
     <t>f_animProfile</t>
+  </si>
+  <si>
+    <t>f_controllerAssetKey</t>
   </si>
   <si>
     <t>int</t>
@@ -123,6 +126,9 @@
     <t>角色使用的动画配置文件</t>
   </si>
   <si>
+    <t>角色使用的动画控制器资源</t>
+  </si>
+  <si>
     <t>战士</t>
   </si>
   <si>
@@ -132,7 +138,7 @@
     <t>攻防兼备，均衡型</t>
   </si>
   <si>
-    <t>BattleAnimationComponent,PlayerSkillComponent,PlayerPropertyComponent,StatusComponent,AnimatorComponent</t>
+    <t>AnimatorComponent,BattleAnimationComponent,PlayerSkillComponent,PlayerPropertyComponent,StatusComponent</t>
   </si>
   <si>
     <t>10,11,12</t>
@@ -141,6 +147,9 @@
     <t>WarriorAnimationConfigCollection</t>
   </si>
   <si>
+    <t>WarriorController</t>
+  </si>
+  <si>
     <t>法师</t>
   </si>
   <si>
@@ -156,6 +165,9 @@
     <t>WizardAnimationConfigCollection</t>
   </si>
   <si>
+    <t>WizardController</t>
+  </si>
+  <si>
     <t>牧师</t>
   </si>
   <si>
@@ -171,6 +183,9 @@
     <t>PriestAnimationConfigCollection</t>
   </si>
   <si>
+    <t>PriestController</t>
+  </si>
+  <si>
     <t>枪手</t>
   </si>
   <si>
@@ -183,6 +198,12 @@
     <t>40,41,42</t>
   </si>
   <si>
+    <t>GunmanAnimationConfigCollection</t>
+  </si>
+  <si>
+    <t>GunmanController</t>
+  </si>
+  <si>
     <t>f_baseToughness</t>
   </si>
   <si>
@@ -240,6 +261,9 @@
     <t>怪物使用的动画配置文件</t>
   </si>
   <si>
+    <t>怪物使用的动画控制器资源</t>
+  </si>
+  <si>
     <t>史莱姆</t>
   </si>
   <si>
@@ -249,7 +273,7 @@
     <t>黏糊糊...</t>
   </si>
   <si>
-    <t>BattleAnimationComponent,MonsterSkillComponent,MonsterPropertyComponent,ToughnessComponent,StatusComponent,AnimatorComponent</t>
+    <t>AnimatorComponent,BattleAnimationComponent,MonsterSkillComponent,MonsterPropertyComponent,ToughnessComponent,StatusComponent,AnimatorComponent</t>
   </si>
   <si>
     <t>1,2,3,4</t>
@@ -258,6 +282,9 @@
     <t>SlimeAnimationCommonConfig</t>
   </si>
   <si>
+    <t>SlimeController</t>
+  </si>
+  <si>
     <t>甲壳虫</t>
   </si>
   <si>
@@ -273,6 +300,9 @@
     <t>TurtleShellAnimationCommonConfig</t>
   </si>
   <si>
+    <t>TurtleShellController</t>
+  </si>
+  <si>
     <t>宝箱怪</t>
   </si>
   <si>
@@ -282,7 +312,10 @@
     <t>里面可能有宝藏</t>
   </si>
   <si>
-    <t>null</t>
+    <t>ChestAnimationCommonConfig</t>
+  </si>
+  <si>
+    <t>ChestController</t>
   </si>
   <si>
     <t>深渊法师</t>
@@ -294,10 +327,16 @@
     <t>邪恶的力量</t>
   </si>
   <si>
+    <t>AnimatorComponent,BattleAnimationComponent,MonsterSkillComponent,MonsterPropertyComponent,ToughnessComponent,StatusComponent</t>
+  </si>
+  <si>
     <t>103,104,105,106</t>
   </si>
   <si>
     <t>AbyssalMageAnimationConfigCollection</t>
+  </si>
+  <si>
+    <t>AbyssalMageController</t>
   </si>
 </sst>
 </file>
@@ -1334,7 +1373,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -1345,10 +1384,11 @@
     <col min="6" max="6" width="90.875" customWidth="1"/>
     <col min="7" max="7" width="14.625" customWidth="1"/>
     <col min="8" max="12" width="15" customWidth="1"/>
-    <col min="13" max="13" width="36" style="4" customWidth="1"/>
+    <col min="13" max="13" width="31.2" style="4" customWidth="1"/>
+    <col min="14" max="14" width="22.625" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="2" customFormat="1" ht="22" customHeight="1" spans="1:13">
+    <row r="1" s="2" customFormat="1" ht="22" customHeight="1" spans="1:14">
       <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
@@ -1388,51 +1428,57 @@
       <c r="M1" s="10" t="s">
         <v>12</v>
       </c>
+      <c r="N1" s="10" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" s="2" customFormat="1" ht="20" customHeight="1" spans="1:13">
+    <row r="2" s="2" customFormat="1" ht="20" customHeight="1" spans="1:14">
       <c r="A2" s="10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B2" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="F2" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="I2" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" s="10" t="s">
+      <c r="J2" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="K2" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="J2" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="10" t="s">
-        <v>13</v>
-      </c>
       <c r="L2" s="10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M2" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="N2" s="10" t="s">
+        <v>15</v>
       </c>
     </row>
-    <row r="3" s="2" customFormat="1" ht="18" customHeight="1" spans="1:13">
+    <row r="3" s="2" customFormat="1" ht="18" customHeight="1" spans="1:14">
       <c r="A3" s="10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3" s="10"/>
       <c r="C3" s="10"/>
@@ -1446,69 +1492,73 @@
       <c r="K3" s="10"/>
       <c r="L3" s="10"/>
       <c r="M3" s="10"/>
+      <c r="N3" s="10"/>
     </row>
-    <row r="4" s="2" customFormat="1" ht="101" customHeight="1" spans="1:13">
+    <row r="4" s="2" customFormat="1" ht="101" customHeight="1" spans="1:14">
       <c r="A4" s="10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J4" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K4" s="10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L4" s="10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M4" s="10" t="s">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="N4" s="10" t="s">
+        <v>30</v>
       </c>
     </row>
-    <row r="5" s="4" customFormat="1" ht="39" customHeight="1" spans="1:13">
+    <row r="5" s="4" customFormat="1" ht="39" customHeight="1" spans="1:14">
       <c r="A5" s="4">
         <v>1</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E5" s="4">
         <v>1</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H5" s="4">
         <v>3000</v>
@@ -1526,30 +1576,33 @@
         <v>50</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>34</v>
+        <v>36</v>
+      </c>
+      <c r="N5" s="4" t="s">
+        <v>37</v>
       </c>
     </row>
-    <row r="6" s="4" customFormat="1" ht="35" customHeight="1" spans="1:13">
+    <row r="6" s="4" customFormat="1" ht="35" customHeight="1" spans="1:14">
       <c r="A6" s="4">
         <v>2</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E6" s="4">
         <v>2</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="H6" s="4">
         <v>2000</v>
@@ -1567,30 +1620,33 @@
         <v>80</v>
       </c>
       <c r="M6" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
+      </c>
+      <c r="N6" s="4" t="s">
+        <v>43</v>
       </c>
     </row>
-    <row r="7" s="4" customFormat="1" ht="38" customHeight="1" spans="1:13">
+    <row r="7" s="4" customFormat="1" ht="38" customHeight="1" spans="1:14">
       <c r="A7" s="4">
         <v>3</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E7" s="4">
         <v>3</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="H7" s="4">
         <v>1000</v>
@@ -1608,30 +1664,33 @@
         <v>60</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>44</v>
+        <v>48</v>
+      </c>
+      <c r="N7" s="4" t="s">
+        <v>49</v>
       </c>
     </row>
-    <row r="8" s="4" customFormat="1" ht="42" customHeight="1" spans="1:13">
+    <row r="8" s="4" customFormat="1" ht="42" customHeight="1" spans="1:14">
       <c r="A8" s="4">
         <v>4</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="E8" s="4">
         <v>4</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="H8" s="4">
         <v>250</v>
@@ -1647,6 +1706,12 @@
       </c>
       <c r="L8" s="4">
         <v>90</v>
+      </c>
+      <c r="M8" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="N8" s="4" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -1659,7 +1724,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O8"/>
+  <dimension ref="A1:P8"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -1673,9 +1738,10 @@
     <col min="12" max="13" width="21.5" customWidth="1"/>
     <col min="14" max="14" width="19.375" style="4" customWidth="1"/>
     <col min="15" max="15" width="40.375" style="4" customWidth="1"/>
+    <col min="16" max="16" width="22.625" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="24" customHeight="1" spans="1:15">
+    <row r="1" s="1" customFormat="1" ht="24" customHeight="1" spans="1:16">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -1710,68 +1776,74 @@
         <v>10</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="M1" s="7" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="N1" s="7" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="O1" s="7" t="s">
         <v>12</v>
       </c>
+      <c r="P1" s="7" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" s="2" customFormat="1" ht="26" customHeight="1" spans="1:15">
+    <row r="2" s="2" customFormat="1" ht="26" customHeight="1" spans="1:16">
       <c r="A2" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B2" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="F2" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="I2" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" s="10" t="s">
+      <c r="J2" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="11" t="s">
+      <c r="K2" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="J2" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="10" t="s">
-        <v>13</v>
-      </c>
       <c r="L2" s="10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M2" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N2" s="10" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="O2" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="P2" s="10" t="s">
+        <v>15</v>
       </c>
     </row>
-    <row r="3" s="2" customFormat="1" ht="25" customHeight="1" spans="1:15">
+    <row r="3" s="2" customFormat="1" ht="25" customHeight="1" spans="1:16">
       <c r="A3" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3" s="10"/>
       <c r="C3" s="10"/>
@@ -1787,72 +1859,76 @@
       <c r="M3" s="10"/>
       <c r="N3" s="10"/>
       <c r="O3" s="10"/>
+      <c r="P3" s="10"/>
     </row>
-    <row r="4" s="3" customFormat="1" ht="60" customHeight="1" spans="1:15">
+    <row r="4" s="3" customFormat="1" ht="60" customHeight="1" spans="1:16">
       <c r="A4" s="12" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="H4" s="13" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="I4" s="13" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="J4" s="13" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="K4" s="13" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="L4" s="13" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="M4" s="13" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="N4" s="13" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="O4" s="13" t="s">
-        <v>67</v>
+        <v>74</v>
+      </c>
+      <c r="P4" s="13" t="s">
+        <v>75</v>
       </c>
     </row>
-    <row r="5" s="4" customFormat="1" ht="86" customHeight="1" spans="1:15">
+    <row r="5" s="4" customFormat="1" ht="86" customHeight="1" spans="1:16">
       <c r="A5" s="4">
         <v>1</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="E5" s="4">
         <v>1</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="G5" s="16">
         <v>101</v>
@@ -1873,33 +1949,36 @@
         <v>50</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="N5" s="4">
         <v>1.75</v>
       </c>
       <c r="O5" s="4" t="s">
-        <v>73</v>
+        <v>81</v>
+      </c>
+      <c r="P5" s="4" t="s">
+        <v>82</v>
       </c>
     </row>
-    <row r="6" s="4" customFormat="1" ht="78" customHeight="1" spans="1:15">
+    <row r="6" s="4" customFormat="1" ht="78" customHeight="1" spans="1:16">
       <c r="A6" s="4">
         <v>2</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="E6" s="4">
         <v>2</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="G6" s="16">
         <v>102</v>
@@ -1920,33 +1999,36 @@
         <v>75</v>
       </c>
       <c r="M6" s="4" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="N6" s="4">
         <v>1.75</v>
       </c>
       <c r="O6" s="4" t="s">
-        <v>78</v>
+        <v>87</v>
+      </c>
+      <c r="P6" s="4" t="s">
+        <v>88</v>
       </c>
     </row>
-    <row r="7" s="4" customFormat="1" ht="54" customHeight="1" spans="1:15">
+    <row r="7" s="4" customFormat="1" ht="54" customHeight="1" spans="1:16">
       <c r="A7" s="4">
         <v>3</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="E7" s="4">
         <v>3</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="G7" s="16">
         <v>103</v>
@@ -1967,36 +2049,39 @@
         <v>100</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="N7" s="4">
         <v>1.75</v>
       </c>
       <c r="O7" s="4" t="s">
-        <v>82</v>
+        <v>92</v>
+      </c>
+      <c r="P7" s="4" t="s">
+        <v>93</v>
       </c>
     </row>
-    <row r="8" s="4" customFormat="1" ht="63" customHeight="1" spans="1:15">
+    <row r="8" s="4" customFormat="1" ht="63" customHeight="1" spans="1:16">
       <c r="A8" s="4">
         <v>4</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="E8" s="4">
         <v>4</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>71</v>
+        <v>97</v>
       </c>
       <c r="G8" s="16" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="H8" s="4">
         <v>200</v>
@@ -2020,7 +2105,10 @@
         <v>2.5</v>
       </c>
       <c r="O8" s="4" t="s">
-        <v>87</v>
+        <v>99</v>
+      </c>
+      <c r="P8" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
